--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Inventory_Valuation_Summary.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Inventory_Valuation_Summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>As of June 30, 2026</t>
+          <t>As of Jun 30, 2026</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>SKU</t>
@@ -466,35 +467,49 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Drivetrain</t>
-        </is>
+          <t>11-Speed Chain 116L</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KV-CHN-11</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>240</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>4104</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>17.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   11-Speed Chain 116L</t>
+          <t>11-Speed Rear Derailleur</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KV-CHN-11</t>
+          <t>KV-DER-11S</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>4104</v>
+        <v>4620</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>17.1</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   12-Speed Chain 126L</t>
+          <t>12-Speed Chain 126L</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,452 +530,381 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   11-Speed Rear Derailleur</t>
+          <t>29in Inner Tube</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KV-DER-11S</t>
+          <t>KV-TUBE-29</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42</v>
+        <v>420</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>4620</v>
+        <v>2520</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Cassette 11-34T</t>
+          <t>29x2.4 Trail Tire</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KV-CAS-1134</t>
+          <t>KV-TIR-2924</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>3776</v>
+        <v>6452.5</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>59</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Crankset 172.5mm</t>
+          <t>700c Wheelset</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KV-CRK-172</t>
+          <t>KV-WHL-700</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>3654</v>
+        <v>6240</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>174</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Bottom Bracket BSA</t>
+          <t>700x32 Tire</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KV-BB-BSA</t>
+          <t>KV-TIR-70032</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1672</v>
+        <v>6975</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>19</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total Drivetrain</t>
+          <t>Bottom Bracket BSA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KV-BB-BSA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>573</v>
+        <v>88</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>20894</v>
+        <v>1672</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Wheels &amp; Tires</t>
-        </is>
+          <t>Carbon Handlebar 780mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KV-BAR-780</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>2185</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Disc Hub, Rear</t>
+          <t>Cassette 11-34T</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KV-HUB-DT</t>
+          <t>KV-CAS-1134</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>850</v>
+        <v>3776</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>212.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   700x32 Tire</t>
+          <t>Comp Saddle</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KV-TIR-70032</t>
+          <t>KV-SAD-CMP</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>6975</v>
+        <v>1512</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>22.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   29x2.4 Trail Tire</t>
+          <t>Crankset 172.5mm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KV-TIR-2924</t>
+          <t>KV-CRK-172</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>6452.5</v>
+        <v>3654</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>44.5</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   29in Inner Tube</t>
+          <t>Disc Brake Pads</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KV-TUBE-29</t>
+          <t>KV-BRK-PAD</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2520</v>
+        <v>3230</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   700c Wheelset</t>
+          <t>Disc Hub, Rear</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KV-WHL-700</t>
+          <t>KV-HUB-DT</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>6240</v>
+        <v>850</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>390</v>
+        <v>212.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Tubeless Sealant 1L</t>
+          <t>Dropper Post 150mm</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KV-SEAL-1L</t>
+          <t>KV-DRP-150</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>1488</v>
+        <v>4715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>15.5</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Total Wheels &amp; Tires</t>
+          <t>Flat Pedals</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KV-PED-FLT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>991</v>
+        <v>74</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>24525.5</v>
+        <v>2442</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Components</t>
-        </is>
+          <t>Hydraulic Brake Set</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KV-BRK-HYD</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>26</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>4498</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>173</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Disc Brake Pads</t>
+          <t>Lock-On Grips</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KV-BRK-PAD</t>
+          <t>KV-GRP-LCK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>380</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>3230</v>
+        <v>612.4</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>8.5</v>
+        <v>16.55135135135135</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Hydraulic Brake Set</t>
+          <t>Stem 50mm</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KV-BRK-HYD</t>
+          <t>KV-STM-50</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>4498</v>
+        <v>1740</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>173</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Lock-On Grips</t>
+          <t>Tubeless Sealant 1L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KV-GRP-LCK</t>
+          <t>KV-SEAL-1L</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>612.4</v>
+        <v>1488</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>16.55135135135135</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Carbon Handlebar 780mm</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>KV-BAR-780</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>2217</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>2185</v>
+        <v>66353.89999999999</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Dropper Post 150mm</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>KV-DRP-150</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>23</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>4715</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Comp Saddle</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>KV-SAD-CMP</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>36</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Flat Pedals</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>KV-PED-FLT</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>74</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>2442</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>33</v>
-      </c>
-    </row>
+        <v>29.92958953540821</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Stem 50mm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>KV-STM-50</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>58</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>1740</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Total Components</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>653</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>20934.4</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2217</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>66353.89999999999</v>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
         <is>
           <t>Accrual Basis Wednesday, July 15, 2026 10:42 AM GMTZ</t>
         </is>
